--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497217</v>
+        <v>121497089</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>57504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504840</v>
+        <v>504833</v>
       </c>
       <c r="R2" t="n">
-        <v>7010987</v>
+        <v>7010908</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +780,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,26 +791,6 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497010</v>
+        <v>121497118</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>90710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,61 +820,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504920</v>
+        <v>504876</v>
       </c>
       <c r="R3" t="n">
-        <v>7011117</v>
+        <v>7011032</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -920,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,6 +916,26 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -958,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497211</v>
+        <v>121497010</v>
       </c>
       <c r="B4" t="n">
-        <v>90706</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,53 +965,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504869</v>
+        <v>504920</v>
       </c>
       <c r="R4" t="n">
-        <v>7011055</v>
+        <v>7011117</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,27 +1073,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1111,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121496472</v>
+        <v>121497217</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,58 +1103,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504851</v>
+        <v>504840</v>
       </c>
       <c r="R5" t="n">
-        <v>7011045</v>
+        <v>7010987</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1211,7 +1178,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1231,7 +1198,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1249,10 +1236,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497089</v>
+        <v>121496472</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1261,39 +1248,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1301,17 +1292,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504833</v>
+        <v>504851</v>
       </c>
       <c r="R6" t="n">
-        <v>7010908</v>
+        <v>7011045</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1345,7 +1336,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1354,6 +1345,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1364,7 +1356,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1382,10 +1374,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497118</v>
+        <v>121497211</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>90706</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1398,25 +1390,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504876</v>
+        <v>504869</v>
       </c>
       <c r="R7" t="n">
-        <v>7011032</v>
+        <v>7011055</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497089</v>
+        <v>121497217</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,53 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504833</v>
+        <v>504840</v>
       </c>
       <c r="R2" t="n">
-        <v>7010908</v>
+        <v>7010987</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,6 +783,26 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,7 +823,7 @@
         <v>121497118</v>
       </c>
       <c r="B3" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -953,10 +965,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497010</v>
+        <v>121497211</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,58 +977,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504920</v>
+        <v>504869</v>
       </c>
       <c r="R4" t="n">
-        <v>7011117</v>
+        <v>7011055</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1053,7 +1060,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,7 +1080,27 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1091,10 +1118,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497217</v>
+        <v>121496472</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,45 +1130,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504840</v>
+        <v>504851</v>
       </c>
       <c r="R5" t="n">
-        <v>7010987</v>
+        <v>7011045</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1178,7 +1218,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,27 +1238,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1236,10 +1256,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121496472</v>
+        <v>121497010</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1271,7 +1291,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1296,10 +1316,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504851</v>
+        <v>504920</v>
       </c>
       <c r="R6" t="n">
-        <v>7011045</v>
+        <v>7011117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1336,7 +1356,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1374,10 +1394,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497211</v>
+        <v>121497089</v>
       </c>
       <c r="B7" t="n">
-        <v>90706</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1390,52 +1410,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504869</v>
+        <v>504833</v>
       </c>
       <c r="R7" t="n">
-        <v>7011055</v>
+        <v>7010908</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1478,7 +1499,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1490,26 +1510,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497118</v>
+        <v>121497211</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,25 +836,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -867,13 +875,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504876</v>
+        <v>504869</v>
       </c>
       <c r="R3" t="n">
-        <v>7011032</v>
+        <v>7011055</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -927,7 +935,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -965,10 +973,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497211</v>
+        <v>121497089</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,52 +989,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504869</v>
+        <v>504833</v>
       </c>
       <c r="R4" t="n">
-        <v>7011055</v>
+        <v>7010908</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1069,7 +1078,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1081,26 +1089,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1118,7 +1106,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121496472</v>
+        <v>121497010</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1153,7 +1141,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1178,10 +1166,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504851</v>
+        <v>504920</v>
       </c>
       <c r="R5" t="n">
-        <v>7011045</v>
+        <v>7011117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1218,7 +1206,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1256,7 +1244,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497010</v>
+        <v>121496472</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1291,7 +1279,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1316,10 +1304,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504920</v>
+        <v>504851</v>
       </c>
       <c r="R6" t="n">
-        <v>7011117</v>
+        <v>7011045</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1356,7 +1344,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1394,10 +1382,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497089</v>
+        <v>121497118</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1410,50 +1398,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504833</v>
+        <v>504876</v>
       </c>
       <c r="R7" t="n">
-        <v>7010908</v>
+        <v>7011032</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1499,6 +1478,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1509,7 +1489,27 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1525,6 +1525,308 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121548345</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504834</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7011084</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121548388</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90710</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gnagmyrmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504891</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7011076</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497217</v>
+        <v>121497010</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504840</v>
+        <v>504920</v>
       </c>
       <c r="R2" t="n">
-        <v>7010987</v>
+        <v>7011117</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,27 +795,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -823,7 +816,7 @@
         <v>121497211</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -973,10 +966,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497089</v>
+        <v>121497118</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,50 +982,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504833</v>
+        <v>504876</v>
       </c>
       <c r="R4" t="n">
-        <v>7010908</v>
+        <v>7011032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1078,6 +1062,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1088,7 +1073,27 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1106,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497010</v>
+        <v>121497089</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>57508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,43 +1123,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1162,17 +1163,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504920</v>
+        <v>504833</v>
       </c>
       <c r="R5" t="n">
-        <v>7011117</v>
+        <v>7010908</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1206,7 +1207,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,7 +1216,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121496472</v>
+        <v>121497217</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>90737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1256,58 +1256,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504851</v>
+        <v>504840</v>
       </c>
       <c r="R6" t="n">
-        <v>7011045</v>
+        <v>7010987</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1344,7 +1331,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1364,7 +1351,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1382,10 +1389,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497118</v>
+        <v>121496472</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1394,48 +1401,61 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504876</v>
+        <v>504851</v>
       </c>
       <c r="R7" t="n">
-        <v>7011032</v>
+        <v>7011045</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1469,7 +1489,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1490,26 +1510,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548345</v>
+        <v>121548388</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>90715</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1543,46 +1543,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504834</v>
+        <v>504891</v>
       </c>
       <c r="R8" t="n">
-        <v>7011084</v>
+        <v>7011076</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1628,17 +1631,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1653,12 +1657,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1676,10 +1680,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548388</v>
+        <v>121548338</v>
       </c>
       <c r="B9" t="n">
-        <v>90710</v>
+        <v>57371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1692,49 +1696,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504891</v>
+        <v>504834</v>
       </c>
       <c r="R9" t="n">
-        <v>7011076</v>
+        <v>7011084</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1780,18 +1781,17 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497010</v>
+        <v>121497217</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,58 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504920</v>
+        <v>504840</v>
       </c>
       <c r="R2" t="n">
-        <v>7011117</v>
+        <v>7010987</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +782,27 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,7 +823,7 @@
         <v>121497211</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>90716</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -969,7 +976,7 @@
         <v>121497118</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1111,10 +1118,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497089</v>
+        <v>121497010</v>
       </c>
       <c r="B5" t="n">
-        <v>57508</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,39 +1130,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1163,17 +1174,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504833</v>
+        <v>504920</v>
       </c>
       <c r="R5" t="n">
-        <v>7010908</v>
+        <v>7011117</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1207,7 +1218,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1216,6 +1227,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1226,7 +1238,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1244,10 +1256,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497217</v>
+        <v>121496472</v>
       </c>
       <c r="B6" t="n">
-        <v>90737</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1256,45 +1268,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504840</v>
+        <v>504851</v>
       </c>
       <c r="R6" t="n">
-        <v>7010987</v>
+        <v>7011045</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1331,7 +1356,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1351,27 +1376,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121496472</v>
+        <v>121497089</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1401,43 +1406,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1445,17 +1446,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504851</v>
+        <v>504833</v>
       </c>
       <c r="R7" t="n">
-        <v>7011045</v>
+        <v>7010908</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1489,7 +1490,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1498,7 +1499,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548388</v>
+        <v>121548345</v>
       </c>
       <c r="B8" t="n">
-        <v>90715</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1543,49 +1543,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504891</v>
+        <v>504834</v>
       </c>
       <c r="R8" t="n">
-        <v>7011076</v>
+        <v>7011084</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1631,18 +1628,17 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1657,12 +1653,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1680,10 +1676,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548338</v>
+        <v>121548388</v>
       </c>
       <c r="B9" t="n">
-        <v>57371</v>
+        <v>90716</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1696,46 +1692,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504834</v>
+        <v>504891</v>
       </c>
       <c r="R9" t="n">
-        <v>7011084</v>
+        <v>7011076</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1781,17 +1780,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497217</v>
+        <v>121497118</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504840</v>
+        <v>504876</v>
       </c>
       <c r="R2" t="n">
-        <v>7010987</v>
+        <v>7011032</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497211</v>
+        <v>121497010</v>
       </c>
       <c r="B3" t="n">
-        <v>90716</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,53 +832,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504869</v>
+        <v>504920</v>
       </c>
       <c r="R3" t="n">
-        <v>7011055</v>
+        <v>7011117</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -915,7 +920,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,27 +940,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -973,10 +958,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497118</v>
+        <v>121496472</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -985,48 +970,61 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504876</v>
+        <v>504851</v>
       </c>
       <c r="R4" t="n">
-        <v>7011032</v>
+        <v>7011045</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1060,7 +1058,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,26 +1079,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1118,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497010</v>
+        <v>121497211</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>90716</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1130,58 +1108,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504920</v>
+        <v>504869</v>
       </c>
       <c r="R5" t="n">
-        <v>7011117</v>
+        <v>7011055</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1218,7 +1191,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1238,7 +1211,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1256,10 +1249,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121496472</v>
+        <v>121497089</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1268,43 +1261,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1312,17 +1301,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504851</v>
+        <v>504833</v>
       </c>
       <c r="R6" t="n">
-        <v>7011045</v>
+        <v>7010908</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1356,7 +1345,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,7 +1354,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1376,7 +1364,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1394,10 +1382,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497089</v>
+        <v>121497217</v>
       </c>
       <c r="B7" t="n">
-        <v>57509</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1410,53 +1398,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504833</v>
+        <v>504840</v>
       </c>
       <c r="R7" t="n">
-        <v>7010908</v>
+        <v>7010987</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1499,6 +1478,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1510,6 +1490,26 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548345</v>
+        <v>121548388</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>90716</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1543,46 +1543,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504834</v>
+        <v>504891</v>
       </c>
       <c r="R8" t="n">
-        <v>7011084</v>
+        <v>7011076</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1628,17 +1631,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1653,12 +1657,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1676,10 +1680,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548388</v>
+        <v>121548338</v>
       </c>
       <c r="B9" t="n">
-        <v>90716</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1692,49 +1696,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504891</v>
+        <v>504834</v>
       </c>
       <c r="R9" t="n">
-        <v>7011076</v>
+        <v>7011084</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1780,18 +1781,17 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497010</v>
+        <v>121497089</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,43 +832,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -876,17 +872,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504920</v>
+        <v>504833</v>
       </c>
       <c r="R3" t="n">
-        <v>7011117</v>
+        <v>7010908</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -920,7 +916,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +925,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -940,7 +935,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -958,7 +953,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121496472</v>
+        <v>121497010</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1018,10 +1013,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504851</v>
+        <v>504920</v>
       </c>
       <c r="R4" t="n">
-        <v>7011045</v>
+        <v>7011117</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1058,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1096,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497211</v>
+        <v>121497217</v>
       </c>
       <c r="B5" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,33 +1107,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1151,10 +1138,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504869</v>
+        <v>504840</v>
       </c>
       <c r="R5" t="n">
-        <v>7011055</v>
+        <v>7010987</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1226,12 +1213,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1249,10 +1236,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497089</v>
+        <v>121497211</v>
       </c>
       <c r="B6" t="n">
-        <v>57509</v>
+        <v>90716</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1265,53 +1252,52 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504833</v>
+        <v>504869</v>
       </c>
       <c r="R6" t="n">
-        <v>7010908</v>
+        <v>7011055</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1354,6 +1340,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1365,6 +1352,26 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1382,10 +1389,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497217</v>
+        <v>121496472</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1394,45 +1401,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504840</v>
+        <v>504851</v>
       </c>
       <c r="R7" t="n">
-        <v>7010987</v>
+        <v>7011045</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1469,7 +1489,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1489,27 +1509,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548338</v>
+        <v>121548345</v>
       </c>
       <c r="B9" t="n">
         <v>57372</v>
@@ -1718,7 +1718,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497118</v>
+        <v>121497211</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>90716</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,25 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -722,13 +730,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504876</v>
+        <v>504869</v>
       </c>
       <c r="R2" t="n">
-        <v>7011032</v>
+        <v>7011055</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +790,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -820,10 +828,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497089</v>
+        <v>121497217</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,53 +844,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504833</v>
+        <v>504840</v>
       </c>
       <c r="R3" t="n">
-        <v>7010908</v>
+        <v>7010987</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -925,6 +924,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -936,6 +936,26 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,7 +973,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497010</v>
+        <v>121496472</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -988,7 +1008,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1013,10 +1033,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504920</v>
+        <v>504851</v>
       </c>
       <c r="R4" t="n">
-        <v>7011117</v>
+        <v>7011045</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1053,7 +1073,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1091,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497217</v>
+        <v>121497089</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,44 +1127,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504840</v>
+        <v>504833</v>
       </c>
       <c r="R5" t="n">
-        <v>7010987</v>
+        <v>7010908</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1187,7 +1216,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1199,26 +1227,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1236,10 +1244,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497211</v>
+        <v>121497118</v>
       </c>
       <c r="B6" t="n">
-        <v>90716</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1252,33 +1260,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504869</v>
+        <v>504876</v>
       </c>
       <c r="R6" t="n">
-        <v>7011055</v>
+        <v>7011032</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121496472</v>
+        <v>121497010</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504851</v>
+        <v>504920</v>
       </c>
       <c r="R7" t="n">
-        <v>7011045</v>
+        <v>7011117</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1680,7 +1680,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548345</v>
+        <v>121548338</v>
       </c>
       <c r="B9" t="n">
         <v>57372</v>
@@ -1718,7 +1718,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121496472</v>
+        <v>121497010</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504851</v>
+        <v>504920</v>
       </c>
       <c r="R2" t="n">
-        <v>7011045</v>
+        <v>7011117</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497211</v>
+        <v>121497118</v>
       </c>
       <c r="B3" t="n">
-        <v>90724</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,33 +829,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -868,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504869</v>
+        <v>504876</v>
       </c>
       <c r="R3" t="n">
-        <v>7011055</v>
+        <v>7011032</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -928,7 +920,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1099,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497010</v>
+        <v>121497217</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,58 +1103,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504920</v>
+        <v>504840</v>
       </c>
       <c r="R5" t="n">
-        <v>7011117</v>
+        <v>7010987</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1199,7 +1178,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1219,7 +1198,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,10 +1236,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497217</v>
+        <v>121497211</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>90724</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,25 +1252,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1284,10 +1291,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504840</v>
+        <v>504869</v>
       </c>
       <c r="R6" t="n">
-        <v>7010987</v>
+        <v>7011055</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1359,12 +1366,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1382,10 +1389,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497118</v>
+        <v>121496472</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1394,48 +1401,61 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504876</v>
+        <v>504851</v>
       </c>
       <c r="R7" t="n">
-        <v>7011032</v>
+        <v>7011045</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1469,7 +1489,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1490,26 +1510,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548345</v>
+        <v>121548338</v>
       </c>
       <c r="B8" t="n">
         <v>57373</v>
@@ -1565,7 +1565,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">

--- a/artfynd/A 54508-2024 artfynd.xlsx
+++ b/artfynd/A 54508-2024 artfynd.xlsx
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497118</v>
+        <v>121497089</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,41 +829,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504876</v>
+        <v>504833</v>
       </c>
       <c r="R3" t="n">
-        <v>7011032</v>
+        <v>7010908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,7 +918,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -920,27 +928,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -958,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497089</v>
+        <v>121497217</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,53 +962,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504833</v>
+        <v>504840</v>
       </c>
       <c r="R4" t="n">
-        <v>7010908</v>
+        <v>7010987</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1063,6 +1042,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1074,6 +1054,26 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497217</v>
+        <v>121497118</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,21 +1107,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504840</v>
+        <v>504876</v>
       </c>
       <c r="R5" t="n">
-        <v>7010987</v>
+        <v>7011032</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497211</v>
+        <v>121496472</v>
       </c>
       <c r="B6" t="n">
-        <v>90724</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,53 +1248,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504869</v>
+        <v>504851</v>
       </c>
       <c r="R6" t="n">
-        <v>7011055</v>
+        <v>7011045</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1331,7 +1336,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1351,27 +1356,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1389,10 +1374,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121496472</v>
+        <v>121497211</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>90724</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1401,58 +1386,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504851</v>
+        <v>504869</v>
       </c>
       <c r="R7" t="n">
-        <v>7011045</v>
+        <v>7011055</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1489,7 +1469,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1509,7 +1489,27 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548338</v>
+        <v>121548388</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>90724</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1543,46 +1543,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504834</v>
+        <v>504891</v>
       </c>
       <c r="R8" t="n">
-        <v>7011084</v>
+        <v>7011076</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1628,17 +1631,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1653,12 +1657,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1676,10 +1680,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548388</v>
+        <v>121548338</v>
       </c>
       <c r="B9" t="n">
-        <v>90724</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1692,49 +1696,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504891</v>
+        <v>504834</v>
       </c>
       <c r="R9" t="n">
-        <v>7011076</v>
+        <v>7011084</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1780,18 +1781,17 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
